--- a/chi_tiet_cong_trinh.xlsx
+++ b/chi_tiet_cong_trinh.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,16 @@
           <t>GT gói thầu trúng</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Số hợp đồng</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Giá trị hợp đồng</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -608,6 +618,14 @@
       </c>
       <c r="E2" t="n">
         <v>11333808687</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11-2026/HĐXL/LDLTQV-PCVT, ngày 27/03/2026</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9368774129</v>
       </c>
     </row>
     <row r="3">
@@ -624,6 +642,10 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/chi_tiet_cong_trinh.xlsx
+++ b/chi_tiet_cong_trinh.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,10 +465,106 @@
           <t>VTAD2605001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>111/QĐ_PCVT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46110</v>
+      </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>13254.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>01/PAKT-QLHTĐĐ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>45945</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13650.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VTAD2608001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>127/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="D4" t="n">
+        <v>523.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VTAD2610001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>108/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13236.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VTAD2610002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>128/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5069.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>129/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3311621013</v>
       </c>
     </row>
   </sheetData>
@@ -482,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,16 +619,22 @@
           <t>XL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>115/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46090</v>
+      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>11333.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2606001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,9 +642,101 @@
           <t>TB</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46031</v>
+      </c>
       <c r="E3" t="n">
+        <v>11705.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VTAD2610001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>118/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13236.6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VTAD2610002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>160/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5069.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>161/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2579.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -557,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,42 +804,98 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115/QĐ-PCVT</t>
+          <t>1292/TM-PCVT</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46090</v>
+        <v>46107</v>
       </c>
       <c r="E2" t="n">
-        <v>11333808687</v>
+        <v>9368.799999999999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11-2026/HĐXL/LDLTQV-PCVT, ngày 27/03/2026</t>
+          <t>11-2026/HĐXL/LDLTQV-PCVT</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9368774129</v>
+        <v>9368.799999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VTAD2605001</t>
+          <t>VTAD2610002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>4827.7</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1314/HĐ-PCVT</t>
+        </is>
+      </c>
       <c r="G3" t="n">
+        <v>4827.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>166/QĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2412.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1313/HĐ-PCVT</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>2412.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -751,7 +1001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +1031,84 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VTAD2606001</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VTAD2607001</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VTAD2608001</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VTAD2610001</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VTAD2610002</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,6 +1160,18 @@
       </c>
       <c r="D2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VTAD2606002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
